--- a/datos_terraplen.xlsx
+++ b/datos_terraplen.xlsx
@@ -431,25 +431,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
-        <v>14.72</v>
+        <v>7.5</v>
       </c>
       <c r="B2" s="1">
-        <v>20.72</v>
+        <v>17.5</v>
       </c>
       <c r="C2" s="1">
-        <v>9.81</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1">
         <v>18</v>
       </c>
       <c r="E2" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
